--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/104.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/104.xlsx
@@ -426,13 +426,13 @@
         <v>-20.32181652651279</v>
       </c>
       <c r="E2">
-        <v>-8.956168903007613</v>
+        <v>-12.36748195840772</v>
       </c>
       <c r="F2">
-        <v>-4.252178969365093</v>
+        <v>-5.516189298331398</v>
       </c>
       <c r="G2">
-        <v>-10.2313149717878</v>
+        <v>-11.49207665059953</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.5736453438308</v>
       </c>
       <c r="E3">
-        <v>-9.116549338463267</v>
+        <v>-13.81724121264533</v>
       </c>
       <c r="F3">
-        <v>-4.413167426787259</v>
+        <v>-5.048478181442413</v>
       </c>
       <c r="G3">
-        <v>-10.45331022401471</v>
+        <v>-11.73422650406952</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.79291587668692</v>
       </c>
       <c r="E4">
-        <v>-10.24900294745742</v>
+        <v>-15.03600753622568</v>
       </c>
       <c r="F4">
-        <v>-4.368807824095801</v>
+        <v>-5.066313877462092</v>
       </c>
       <c r="G4">
-        <v>-10.04205439385321</v>
+        <v>-11.76664005544452</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.09431823295405</v>
       </c>
       <c r="E5">
-        <v>-10.75725622770831</v>
+        <v>-15.50639824529843</v>
       </c>
       <c r="F5">
-        <v>-4.247330453704976</v>
+        <v>-4.92709029043581</v>
       </c>
       <c r="G5">
-        <v>-11.05637244163051</v>
+        <v>-12.18032251548631</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.48649511513061</v>
       </c>
       <c r="E6">
-        <v>-10.80286248943955</v>
+        <v>-14.75797281757674</v>
       </c>
       <c r="F6">
-        <v>-3.979509154492053</v>
+        <v>-4.952310807139184</v>
       </c>
       <c r="G6">
-        <v>-10.42661729533157</v>
+        <v>-13.11270787171219</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.97980359582304</v>
       </c>
       <c r="E7">
-        <v>-12.2157418513587</v>
+        <v>-16.67375733194371</v>
       </c>
       <c r="F7">
-        <v>-4.017008935010786</v>
+        <v>-4.83864981729401</v>
       </c>
       <c r="G7">
-        <v>-11.54067545911603</v>
+        <v>-11.843772455964</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.56977179631168</v>
       </c>
       <c r="E8">
-        <v>-12.03113860843602</v>
+        <v>-18.02574230388171</v>
       </c>
       <c r="F8">
-        <v>-3.813307929049218</v>
+        <v>-4.987945773942487</v>
       </c>
       <c r="G8">
-        <v>-11.0050755384995</v>
+        <v>-12.0204893768503</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.24632918959444</v>
       </c>
       <c r="E9">
-        <v>-12.88345628684168</v>
+        <v>-17.65140958545967</v>
       </c>
       <c r="F9">
-        <v>-3.94624578729712</v>
+        <v>-5.004115411339123</v>
       </c>
       <c r="G9">
-        <v>-11.04282237873827</v>
+        <v>-12.8994988073465</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.96489774438854</v>
       </c>
       <c r="E10">
-        <v>-15.06761628479922</v>
+        <v>-18.56423220508181</v>
       </c>
       <c r="F10">
-        <v>-3.645237138773206</v>
+        <v>-4.561110898583951</v>
       </c>
       <c r="G10">
-        <v>-10.23130835069672</v>
+        <v>-13.43025208929354</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.69281188769493</v>
       </c>
       <c r="E11">
-        <v>-15.65714208806576</v>
+        <v>-20.3333213324443</v>
       </c>
       <c r="F11">
-        <v>-3.414403291215372</v>
+        <v>-4.356214986509183</v>
       </c>
       <c r="G11">
-        <v>-10.77311554419938</v>
+        <v>-12.41581155133129</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.3797526939419</v>
       </c>
       <c r="E12">
-        <v>-15.31546419571303</v>
+        <v>-19.82432991093017</v>
       </c>
       <c r="F12">
-        <v>-3.483853546725138</v>
+        <v>-4.642847544585696</v>
       </c>
       <c r="G12">
-        <v>-10.61577855689998</v>
+        <v>-12.30576570706037</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.96057480276248</v>
       </c>
       <c r="E13">
-        <v>-16.86412985075217</v>
+        <v>-19.34492753858216</v>
       </c>
       <c r="F13">
-        <v>-3.2695852630428</v>
+        <v>-4.33118926563341</v>
       </c>
       <c r="G13">
-        <v>-9.837532200982572</v>
+        <v>-12.72574482471786</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.39561805929411</v>
       </c>
       <c r="E14">
-        <v>-16.75066440601598</v>
+        <v>-21.30228797281355</v>
       </c>
       <c r="F14">
-        <v>-3.474374274968275</v>
+        <v>-4.822541944428075</v>
       </c>
       <c r="G14">
-        <v>-10.1870827728376</v>
+        <v>-11.19665349831158</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.64839102427843</v>
       </c>
       <c r="E15">
-        <v>-18.22291659064969</v>
+        <v>-21.2000033304023</v>
       </c>
       <c r="F15">
-        <v>-3.251175473628774</v>
+        <v>-4.116621661533054</v>
       </c>
       <c r="G15">
-        <v>-9.395379049303052</v>
+        <v>-10.67986740799473</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.70120125342314</v>
       </c>
       <c r="E16">
-        <v>-18.46897122585646</v>
+        <v>-21.88772003557715</v>
       </c>
       <c r="F16">
-        <v>-2.883940994838929</v>
+        <v>-3.617211087040632</v>
       </c>
       <c r="G16">
-        <v>-8.581650266295734</v>
+        <v>-10.92703604850226</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.58021205489563</v>
       </c>
       <c r="E17">
-        <v>-19.8221019017184</v>
+        <v>-22.96864866731204</v>
       </c>
       <c r="F17">
-        <v>-2.754353466455139</v>
+        <v>-3.66490122327226</v>
       </c>
       <c r="G17">
-        <v>-7.420479728941904</v>
+        <v>-9.559767498601103</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.3273879149392</v>
       </c>
       <c r="E18">
-        <v>-21.13971575593818</v>
+        <v>-24.29851657219658</v>
       </c>
       <c r="F18">
-        <v>-2.41645318048402</v>
+        <v>-3.559663173338351</v>
       </c>
       <c r="G18">
-        <v>-7.21236228361562</v>
+        <v>-8.96772277654</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.008736214868215</v>
       </c>
       <c r="E19">
-        <v>-20.99889379972166</v>
+        <v>-24.17152004712547</v>
       </c>
       <c r="F19">
-        <v>-2.173313937963221</v>
+        <v>-3.468094881013558</v>
       </c>
       <c r="G19">
-        <v>-6.93482600887636</v>
+        <v>-8.265582552024895</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.712384476279467</v>
       </c>
       <c r="E20">
-        <v>-22.99056195303515</v>
+        <v>-24.84825067435772</v>
       </c>
       <c r="F20">
-        <v>-2.011008629072367</v>
+        <v>-3.361728440614898</v>
       </c>
       <c r="G20">
-        <v>-5.81390177364345</v>
+        <v>-8.034609100295484</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.516054566416178</v>
       </c>
       <c r="E21">
-        <v>-23.0677543209699</v>
+        <v>-26.37907414180664</v>
       </c>
       <c r="F21">
-        <v>-1.802727545603348</v>
+        <v>-2.441301526297265</v>
       </c>
       <c r="G21">
-        <v>-5.379263560338075</v>
+        <v>-7.02675985850192</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.498874386629282</v>
       </c>
       <c r="E22">
-        <v>-23.94438537632275</v>
+        <v>-27.78150178571608</v>
       </c>
       <c r="F22">
-        <v>-1.319875408309804</v>
+        <v>-2.765136920033366</v>
       </c>
       <c r="G22">
-        <v>-5.806943006919902</v>
+        <v>-7.573506385949175</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.724965003741532</v>
       </c>
       <c r="E23">
-        <v>-24.63885403624304</v>
+        <v>-27.47011032752664</v>
       </c>
       <c r="F23">
-        <v>-1.609952526752397</v>
+        <v>-2.637407870541344</v>
       </c>
       <c r="G23">
-        <v>-5.710824627732703</v>
+        <v>-6.892096797600987</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.221385860902529</v>
       </c>
       <c r="E24">
-        <v>-25.00246785668893</v>
+        <v>-27.42737964679026</v>
       </c>
       <c r="F24">
-        <v>-1.096598213527489</v>
+        <v>-2.731705680011397</v>
       </c>
       <c r="G24">
-        <v>-5.062235787860849</v>
+        <v>-6.521904974308604</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.996937547653468</v>
       </c>
       <c r="E25">
-        <v>-25.39972823901181</v>
+        <v>-28.04170790219682</v>
       </c>
       <c r="F25">
-        <v>-1.392891377688182</v>
+        <v>-2.536690509143056</v>
       </c>
       <c r="G25">
-        <v>-4.899178177869586</v>
+        <v>-6.614229468307799</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.024691295144318</v>
       </c>
       <c r="E26">
-        <v>-25.95364665115605</v>
+        <v>-28.19999165418692</v>
       </c>
       <c r="F26">
-        <v>-1.136821968220778</v>
+        <v>-2.158318618502883</v>
       </c>
       <c r="G26">
-        <v>-5.453578686603635</v>
+        <v>-7.155324894519517</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.244993002162651</v>
       </c>
       <c r="E27">
-        <v>-26.54864737949786</v>
+        <v>-28.48802071497078</v>
       </c>
       <c r="F27">
-        <v>-1.244498925264463</v>
+        <v>-2.289911910428577</v>
       </c>
       <c r="G27">
-        <v>-5.413481359031982</v>
+        <v>-7.637101965758575</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.59633283404508</v>
       </c>
       <c r="E28">
-        <v>-26.50379284445189</v>
+        <v>-29.28695221330002</v>
       </c>
       <c r="F28">
-        <v>-1.197857994201814</v>
+        <v>-2.4970598523151</v>
       </c>
       <c r="G28">
-        <v>-5.46000445549536</v>
+        <v>-6.906868451797215</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.001808369222731</v>
       </c>
       <c r="E29">
-        <v>-25.68279409228327</v>
+        <v>-29.64697948233184</v>
       </c>
       <c r="F29">
-        <v>-0.9933683026943569</v>
+        <v>-2.228384935613755</v>
       </c>
       <c r="G29">
-        <v>-6.122497586632153</v>
+        <v>-8.547038512682652</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.383305938261743</v>
       </c>
       <c r="E30">
-        <v>-25.18160070301035</v>
+        <v>-29.24230145958439</v>
       </c>
       <c r="F30">
-        <v>-1.231480070786593</v>
+        <v>-2.470137643605586</v>
       </c>
       <c r="G30">
-        <v>-5.92573200196003</v>
+        <v>-7.752851879993653</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.678243171025019</v>
       </c>
       <c r="E31">
-        <v>-25.72448775247189</v>
+        <v>-28.73621731838318</v>
       </c>
       <c r="F31">
-        <v>-1.14690225637255</v>
+        <v>-2.707443305386864</v>
       </c>
       <c r="G31">
-        <v>-6.31946842512771</v>
+        <v>-8.346525390460076</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.833356868213552</v>
       </c>
       <c r="E32">
-        <v>-25.30294569251988</v>
+        <v>-29.4525992640266</v>
       </c>
       <c r="F32">
-        <v>-0.9829055495640062</v>
+        <v>-2.184542412903687</v>
       </c>
       <c r="G32">
-        <v>-6.223161344844772</v>
+        <v>-8.717816314871497</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.815230679707481</v>
       </c>
       <c r="E33">
-        <v>-25.32789758430215</v>
+        <v>-26.79797610141218</v>
       </c>
       <c r="F33">
-        <v>-1.466999312295255</v>
+        <v>-2.391463092991343</v>
       </c>
       <c r="G33">
-        <v>-6.934312874317773</v>
+        <v>-7.465671986098495</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.613515872200929</v>
       </c>
       <c r="E34">
-        <v>-24.15121889814908</v>
+        <v>-28.39678102066424</v>
       </c>
       <c r="F34">
-        <v>-1.790962986210506</v>
+        <v>-2.877566578529285</v>
       </c>
       <c r="G34">
-        <v>-6.1044782872619</v>
+        <v>-9.135133753915404</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.234365073444217</v>
       </c>
       <c r="E35">
-        <v>-23.92866251456812</v>
+        <v>-27.30059595999752</v>
       </c>
       <c r="F35">
-        <v>-1.363650623518466</v>
+        <v>-2.527924696901099</v>
       </c>
       <c r="G35">
-        <v>-5.961187944685626</v>
+        <v>-8.153169667693403</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.701529522742855</v>
       </c>
       <c r="E36">
-        <v>-23.6822863577068</v>
+        <v>-26.59695261173768</v>
       </c>
       <c r="F36">
-        <v>-1.45526721887368</v>
+        <v>-2.292370613862297</v>
       </c>
       <c r="G36">
-        <v>-6.71692590148153</v>
+        <v>-9.021519141553156</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.054194719940859</v>
       </c>
       <c r="E37">
-        <v>-22.29012023589874</v>
+        <v>-27.23751431707067</v>
       </c>
       <c r="F37">
-        <v>-1.68086929393986</v>
+        <v>-2.779148758120216</v>
       </c>
       <c r="G37">
-        <v>-5.699840237633401</v>
+        <v>-6.83957168207491</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.337270810375842</v>
       </c>
       <c r="E38">
-        <v>-21.95545242130988</v>
+        <v>-25.62970226301735</v>
       </c>
       <c r="F38">
-        <v>-1.729807390432854</v>
+        <v>-3.122820860300153</v>
       </c>
       <c r="G38">
-        <v>-6.448225472786585</v>
+        <v>-7.206926367840137</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.600609152388169</v>
       </c>
       <c r="E39">
-        <v>-22.15654383809449</v>
+        <v>-25.88263565024177</v>
       </c>
       <c r="F39">
-        <v>-1.696441082353418</v>
+        <v>-2.898512672966887</v>
       </c>
       <c r="G39">
-        <v>-6.46451004629426</v>
+        <v>-8.275391698457756</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.894172875021916</v>
       </c>
       <c r="E40">
-        <v>-22.18963792614255</v>
+        <v>-25.46204909830537</v>
       </c>
       <c r="F40">
-        <v>-1.871362192566663</v>
+        <v>-2.718218048582556</v>
       </c>
       <c r="G40">
-        <v>-6.65637602356826</v>
+        <v>-7.495155704671244</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.260377446309269</v>
       </c>
       <c r="E41">
-        <v>-20.96463589385363</v>
+        <v>-24.55120995029859</v>
       </c>
       <c r="F41">
-        <v>-2.047242236711706</v>
+        <v>-2.740521378989691</v>
       </c>
       <c r="G41">
-        <v>-6.405969669523327</v>
+        <v>-7.298366946180347</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.7406219984453986</v>
       </c>
       <c r="E42">
-        <v>-21.08634316128378</v>
+        <v>-23.82420420463318</v>
       </c>
       <c r="F42">
-        <v>-2.220045932116009</v>
+        <v>-2.575351937950764</v>
       </c>
       <c r="G42">
-        <v>-5.635880497814681</v>
+        <v>-7.590039250372295</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.3638932638099424</v>
       </c>
       <c r="E43">
-        <v>-19.89772288917248</v>
+        <v>-24.50785434014916</v>
       </c>
       <c r="F43">
-        <v>-2.03512847016451</v>
+        <v>-2.789697823222958</v>
       </c>
       <c r="G43">
-        <v>-5.830110204603722</v>
+        <v>-7.407899655892673</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.1448952497904211</v>
       </c>
       <c r="E44">
-        <v>-19.15814609966178</v>
+        <v>-24.46404135412494</v>
       </c>
       <c r="F44">
-        <v>-2.163825163970866</v>
+        <v>-2.929579440057105</v>
       </c>
       <c r="G44">
-        <v>-5.167848811654678</v>
+        <v>-7.933316338430403</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.09062362698177168</v>
       </c>
       <c r="E45">
-        <v>-19.43559211668973</v>
+        <v>-23.06012837074099</v>
       </c>
       <c r="F45">
-        <v>-1.931443243880689</v>
+        <v>-3.001676860004528</v>
       </c>
       <c r="G45">
-        <v>-5.030845195057479</v>
+        <v>-7.901164320153002</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1909182381844307</v>
       </c>
       <c r="E46">
-        <v>-18.56489336228693</v>
+        <v>-23.10491497867685</v>
       </c>
       <c r="F46">
-        <v>-1.900567313353282</v>
+        <v>-3.08502967789298</v>
       </c>
       <c r="G46">
-        <v>-5.672865912579419</v>
+        <v>-7.772874059415164</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.428262073479952</v>
       </c>
       <c r="E47">
-        <v>-18.43757078708727</v>
+        <v>-22.51199281990455</v>
       </c>
       <c r="F47">
-        <v>-2.061071156765323</v>
+        <v>-3.358576073990216</v>
       </c>
       <c r="G47">
-        <v>-6.105776021113294</v>
+        <v>-7.84084949097302</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7806053445013611</v>
       </c>
       <c r="E48">
-        <v>-17.99328220219473</v>
+        <v>-22.19302522470028</v>
       </c>
       <c r="F48">
-        <v>-2.157603575282062</v>
+        <v>-3.249908508896423</v>
       </c>
       <c r="G48">
-        <v>-6.107272387697045</v>
+        <v>-7.381292801393551</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.216524765942046</v>
       </c>
       <c r="E49">
-        <v>-17.23642022739675</v>
+        <v>-21.47758973012447</v>
       </c>
       <c r="F49">
-        <v>-2.048908295334749</v>
+        <v>-3.275336491074718</v>
       </c>
       <c r="G49">
-        <v>-5.343291172508355</v>
+        <v>-7.309304988642099</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.709317128099787</v>
       </c>
       <c r="E50">
-        <v>-18.07601289384086</v>
+        <v>-21.19690585418105</v>
       </c>
       <c r="F50">
-        <v>-2.440585691223486</v>
+        <v>-3.264358241668892</v>
       </c>
       <c r="G50">
-        <v>-5.579591292010453</v>
+        <v>-8.221237794526358</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.231588306686951</v>
       </c>
       <c r="E51">
-        <v>-17.13132793110075</v>
+        <v>-20.07072871016153</v>
       </c>
       <c r="F51">
-        <v>-2.252950589921094</v>
+        <v>-3.331702960164082</v>
       </c>
       <c r="G51">
-        <v>-5.345188115102357</v>
+        <v>-7.548124433299582</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.756347113471818</v>
       </c>
       <c r="E52">
-        <v>-15.80707986245973</v>
+        <v>-21.07858588530864</v>
       </c>
       <c r="F52">
-        <v>-2.467179280955546</v>
+        <v>-3.379148413831774</v>
       </c>
       <c r="G52">
-        <v>-4.879036818808659</v>
+        <v>-7.390717924543856</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.266339074888453</v>
       </c>
       <c r="E53">
-        <v>-14.93651696227716</v>
+        <v>-19.48094931235055</v>
       </c>
       <c r="F53">
-        <v>-2.134314387942567</v>
+        <v>-3.233960590327948</v>
       </c>
       <c r="G53">
-        <v>-4.978959014820481</v>
+        <v>-6.642236683570033</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.744193014243159</v>
       </c>
       <c r="E54">
-        <v>-14.92672187299857</v>
+        <v>-19.66575633660358</v>
       </c>
       <c r="F54">
-        <v>-2.401675620587055</v>
+        <v>-2.813996623083546</v>
       </c>
       <c r="G54">
-        <v>-6.408065244849686</v>
+        <v>-8.067588754957704</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.178210041073993</v>
       </c>
       <c r="E55">
-        <v>-14.36443484088817</v>
+        <v>-19.71178374641754</v>
       </c>
       <c r="F55">
-        <v>-2.4579787414398</v>
+        <v>-3.850536104003452</v>
       </c>
       <c r="G55">
-        <v>-4.98773196049955</v>
+        <v>-6.932339789176368</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.564496993046864</v>
       </c>
       <c r="E56">
-        <v>-13.20020040130818</v>
+        <v>-17.70011332341216</v>
       </c>
       <c r="F56">
-        <v>-2.494887007799117</v>
+        <v>-3.809679658796946</v>
       </c>
       <c r="G56">
-        <v>-5.310993490227225</v>
+        <v>-6.426071302037782</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.899441186233119</v>
       </c>
       <c r="E57">
-        <v>-14.09387663282589</v>
+        <v>-18.50701040752089</v>
       </c>
       <c r="F57">
-        <v>-2.376296733292138</v>
+        <v>-3.54294636554793</v>
       </c>
       <c r="G57">
-        <v>-5.909854625553686</v>
+        <v>-7.456892419328348</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.186045871906278</v>
       </c>
       <c r="E58">
-        <v>-13.09511716196019</v>
+        <v>-17.53854189929249</v>
       </c>
       <c r="F58">
-        <v>-2.814972185927457</v>
+        <v>-3.674392372823489</v>
       </c>
       <c r="G58">
-        <v>-5.739139723730089</v>
+        <v>-8.3580427783912</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.430200642880045</v>
       </c>
       <c r="E59">
-        <v>-13.08218384019428</v>
+        <v>-17.76220323053133</v>
       </c>
       <c r="F59">
-        <v>-2.749902460979796</v>
+        <v>-3.630153131781603</v>
       </c>
       <c r="G59">
-        <v>-6.353596839092057</v>
+        <v>-7.821532457751372</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.634886757738021</v>
       </c>
       <c r="E60">
-        <v>-12.87556315664631</v>
+        <v>-17.69572976057274</v>
       </c>
       <c r="F60">
-        <v>-2.709346919897222</v>
+        <v>-3.737639252262479</v>
       </c>
       <c r="G60">
-        <v>-6.749197099398346</v>
+        <v>-8.016507037286749</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.805515382157774</v>
       </c>
       <c r="E61">
-        <v>-12.28018656496186</v>
+        <v>-16.26823701303084</v>
       </c>
       <c r="F61">
-        <v>-2.92191034416159</v>
+        <v>-3.406797543556474</v>
       </c>
       <c r="G61">
-        <v>-6.467559058735928</v>
+        <v>-7.314879947330232</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.945380366988535</v>
       </c>
       <c r="E62">
-        <v>-12.0566927872613</v>
+        <v>-15.38908812612973</v>
       </c>
       <c r="F62">
-        <v>-2.947187874277919</v>
+        <v>-3.559843715812711</v>
       </c>
       <c r="G62">
-        <v>-6.510986795120088</v>
+        <v>-8.774886809422993</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.052031798699103</v>
       </c>
       <c r="E63">
-        <v>-12.26056015861261</v>
+        <v>-15.89293972964516</v>
       </c>
       <c r="F63">
-        <v>-2.673333447380129</v>
+        <v>-4.005143018439355</v>
       </c>
       <c r="G63">
-        <v>-6.761588471351838</v>
+        <v>-8.69017988070966</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.1248882091377</v>
       </c>
       <c r="E64">
-        <v>-11.23932587124684</v>
+        <v>-14.86334587926123</v>
       </c>
       <c r="F64">
-        <v>-2.703523633246152</v>
+        <v>-3.681481832353954</v>
       </c>
       <c r="G64">
-        <v>-7.099595170911426</v>
+        <v>-9.413143436666781</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.160148608796746</v>
       </c>
       <c r="E65">
-        <v>-11.48251398240675</v>
+        <v>-15.33468756787559</v>
       </c>
       <c r="F65">
-        <v>-2.980010179375401</v>
+        <v>-4.229994416901618</v>
       </c>
       <c r="G65">
-        <v>-7.165600827873415</v>
+        <v>-9.294884128912935</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.14989446637519</v>
       </c>
       <c r="E66">
-        <v>-11.16652159462552</v>
+        <v>-14.88652260923248</v>
       </c>
       <c r="F66">
-        <v>-3.356369971650009</v>
+        <v>-3.932785078868843</v>
       </c>
       <c r="G66">
-        <v>-7.505527643845781</v>
+        <v>-8.636290820421404</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.09073571090301</v>
       </c>
       <c r="E67">
-        <v>-11.5622422957858</v>
+        <v>-14.83905967315809</v>
       </c>
       <c r="F67">
-        <v>-3.256856226747455</v>
+        <v>-4.001375382066525</v>
       </c>
       <c r="G67">
-        <v>-8.416603018435369</v>
+        <v>-9.496837338445095</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.978426392828806</v>
       </c>
       <c r="E68">
-        <v>-10.67287717152338</v>
+        <v>-14.57119590713038</v>
       </c>
       <c r="F68">
-        <v>-3.244923002674619</v>
+        <v>-3.660614923212123</v>
       </c>
       <c r="G68">
-        <v>-8.334806059251056</v>
+        <v>-9.805952907083464</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.808127418339113</v>
       </c>
       <c r="E69">
-        <v>-12.07836606386201</v>
+        <v>-15.20443506999296</v>
       </c>
       <c r="F69">
-        <v>-3.108229385848252</v>
+        <v>-4.369783386939711</v>
       </c>
       <c r="G69">
-        <v>-7.903266516570438</v>
+        <v>-9.265820849623674</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.584545403394154</v>
       </c>
       <c r="E70">
-        <v>-10.68903929525676</v>
+        <v>-14.57861807602895</v>
       </c>
       <c r="F70">
-        <v>-3.728822761431227</v>
+        <v>-4.366447310428838</v>
       </c>
       <c r="G70">
-        <v>-8.209925660418667</v>
+        <v>-9.845560273915305</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.314172188334761</v>
       </c>
       <c r="E71">
-        <v>-11.62670512328498</v>
+        <v>-13.86719028094993</v>
       </c>
       <c r="F71">
-        <v>-3.688932376833138</v>
+        <v>-4.687592779667565</v>
       </c>
       <c r="G71">
-        <v>-7.965981491266392</v>
+        <v>-10.06440388678883</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.004389891701894</v>
       </c>
       <c r="E72">
-        <v>-11.67216647384799</v>
+        <v>-17.22994450956579</v>
       </c>
       <c r="F72">
-        <v>-3.848713258494782</v>
+        <v>-4.611303290161973</v>
       </c>
       <c r="G72">
-        <v>-8.811511374723949</v>
+        <v>-10.10445817726847</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.669946491870822</v>
       </c>
       <c r="E73">
-        <v>-11.21506230751374</v>
+        <v>-16.32507389030111</v>
       </c>
       <c r="F73">
-        <v>-3.927142334692132</v>
+        <v>-4.320638616824752</v>
       </c>
       <c r="G73">
-        <v>-7.78602023575161</v>
+        <v>-10.18854272342042</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.32232128710941</v>
       </c>
       <c r="E74">
-        <v>-11.8097958558891</v>
+        <v>-16.00963397634882</v>
       </c>
       <c r="F74">
-        <v>-3.98838265873626</v>
+        <v>-4.478974366838557</v>
       </c>
       <c r="G74">
-        <v>-7.785093283000615</v>
+        <v>-9.247162614964342</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.973025760710943</v>
       </c>
       <c r="E75">
-        <v>-11.22619329662459</v>
+        <v>-15.75360764137716</v>
       </c>
       <c r="F75">
-        <v>-3.430378132784409</v>
+        <v>-4.924139054462389</v>
       </c>
       <c r="G75">
-        <v>-7.891974245735985</v>
+        <v>-9.254071723504801</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.63782660149383</v>
       </c>
       <c r="E76">
-        <v>-11.9900970485045</v>
+        <v>-17.16543186885252</v>
       </c>
       <c r="F76">
-        <v>-3.852528406045075</v>
+        <v>-4.796329235968679</v>
       </c>
       <c r="G76">
-        <v>-8.014818659061721</v>
+        <v>-9.546723949176373</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.326915123316488</v>
       </c>
       <c r="E77">
-        <v>-12.30999750935435</v>
+        <v>-16.71870243646984</v>
       </c>
       <c r="F77">
-        <v>-4.11794959894315</v>
+        <v>-4.692654303773309</v>
       </c>
       <c r="G77">
-        <v>-8.06751592295584</v>
+        <v>-9.637164742763723</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.050594300413958</v>
       </c>
       <c r="E78">
-        <v>-13.58994351677833</v>
+        <v>-17.51299677741522</v>
       </c>
       <c r="F78">
-        <v>-3.921570857281616</v>
+        <v>-4.933014142412512</v>
       </c>
       <c r="G78">
-        <v>-7.208780273342129</v>
+        <v>-8.564650614951576</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.818198818966076</v>
       </c>
       <c r="E79">
-        <v>-14.20464310705351</v>
+        <v>-17.77813893056432</v>
       </c>
       <c r="F79">
-        <v>-4.409358614060627</v>
+        <v>-4.695274545210403</v>
       </c>
       <c r="G79">
-        <v>-7.867108738190518</v>
+        <v>-9.558281063653968</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.630491692568717</v>
       </c>
       <c r="E80">
-        <v>-14.1078152758215</v>
+        <v>-18.47960408282647</v>
       </c>
       <c r="F80">
-        <v>-4.221131998598818</v>
+        <v>-5.20828202683983</v>
       </c>
       <c r="G80">
-        <v>-7.651893483228038</v>
+        <v>-8.656869171493513</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.490857148014449</v>
       </c>
       <c r="E81">
-        <v>-15.01920236918322</v>
+        <v>-18.07198708044804</v>
       </c>
       <c r="F81">
-        <v>-4.350189777353894</v>
+        <v>-5.073541911260158</v>
       </c>
       <c r="G81">
-        <v>-7.212127234882332</v>
+        <v>-8.752295646663006</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.399049252098698</v>
       </c>
       <c r="E82">
-        <v>-15.81980487442128</v>
+        <v>-18.47202341733763</v>
       </c>
       <c r="F82">
-        <v>-4.594460577751275</v>
+        <v>-5.185437860862574</v>
       </c>
       <c r="G82">
-        <v>-6.211256623085553</v>
+        <v>-8.417099600266258</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.349909441540329</v>
       </c>
       <c r="E83">
-        <v>-17.0229660765712</v>
+        <v>-19.75369024488452</v>
       </c>
       <c r="F83">
-        <v>-4.376173640308509</v>
+        <v>-5.351863972545401</v>
       </c>
       <c r="G83">
-        <v>-7.222687875152608</v>
+        <v>-9.516349693853559</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.344804004750753</v>
       </c>
       <c r="E84">
-        <v>-18.00128401576628</v>
+        <v>-19.72716244414759</v>
       </c>
       <c r="F84">
-        <v>-4.667330846185433</v>
+        <v>-5.219322040776359</v>
       </c>
       <c r="G84">
-        <v>-6.815848312740493</v>
+        <v>-8.690530798536823</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.382061105205555</v>
       </c>
       <c r="E85">
-        <v>-18.5808154768979</v>
+        <v>-21.60684596372541</v>
       </c>
       <c r="F85">
-        <v>-4.732726022698715</v>
+        <v>-4.962657949737707</v>
       </c>
       <c r="G85">
-        <v>-7.185599833476152</v>
+        <v>-8.749081106944374</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.459991675884919</v>
       </c>
       <c r="E86">
-        <v>-18.81106120934389</v>
+        <v>-21.68977590822788</v>
       </c>
       <c r="F86">
-        <v>-4.542697149905137</v>
+        <v>-5.121611345058533</v>
       </c>
       <c r="G86">
-        <v>-7.207353428214703</v>
+        <v>-8.519421941794052</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.584115854415118</v>
       </c>
       <c r="E87">
-        <v>-21.118943645665</v>
+        <v>-23.95310268878751</v>
       </c>
       <c r="F87">
-        <v>-4.983422709847992</v>
+        <v>-5.786401993476635</v>
       </c>
       <c r="G87">
-        <v>-6.396769663469692</v>
+        <v>-8.734852382216586</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.755189384187295</v>
       </c>
       <c r="E88">
-        <v>-22.88112232169179</v>
+        <v>-25.71389112329395</v>
       </c>
       <c r="F88">
-        <v>-4.742622600964297</v>
+        <v>-5.207310423260709</v>
       </c>
       <c r="G88">
-        <v>-6.849198748503111</v>
+        <v>-9.297257790064593</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.977420669625636</v>
       </c>
       <c r="E89">
-        <v>-23.33633358589083</v>
+        <v>-24.69827667217169</v>
       </c>
       <c r="F89">
-        <v>-5.037841220661364</v>
+        <v>-5.83262799358944</v>
       </c>
       <c r="G89">
-        <v>-6.332667570192784</v>
+        <v>-8.635416836399036</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.256233345448367</v>
       </c>
       <c r="E90">
-        <v>-24.72215531561414</v>
+        <v>-25.30536842611399</v>
       </c>
       <c r="F90">
-        <v>-5.057255079625778</v>
+        <v>-5.621691035300229</v>
       </c>
       <c r="G90">
-        <v>-6.986093117097513</v>
+        <v>-8.185305133243109</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.589604751581672</v>
       </c>
       <c r="E91">
-        <v>-26.74953501495213</v>
+        <v>-28.58511119769524</v>
       </c>
       <c r="F91">
-        <v>-4.768927164366788</v>
+        <v>-5.544085486178907</v>
       </c>
       <c r="G91">
-        <v>-7.392624798774476</v>
+        <v>-8.530260667889626</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.980103636503963</v>
       </c>
       <c r="E92">
-        <v>-28.65661127380234</v>
+        <v>-32.0828298013987</v>
       </c>
       <c r="F92">
-        <v>-4.738196934783601</v>
+        <v>-5.876272553060077</v>
       </c>
       <c r="G92">
-        <v>-7.283184784337249</v>
+        <v>-8.733170625082636</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.425248246172484</v>
       </c>
       <c r="E93">
-        <v>-30.03898230633181</v>
+        <v>-33.25873411849645</v>
       </c>
       <c r="F93">
-        <v>-4.921613043527263</v>
+        <v>-5.666183669288585</v>
       </c>
       <c r="G93">
-        <v>-6.996137312263662</v>
+        <v>-9.68710101167809</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.913042413783246</v>
       </c>
       <c r="E94">
-        <v>-32.04303130758228</v>
+        <v>-34.11266393364884</v>
       </c>
       <c r="F94">
-        <v>-4.66088674681551</v>
+        <v>-5.371033940798839</v>
       </c>
       <c r="G94">
-        <v>-7.960790555860815</v>
+        <v>-7.775717818033399</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.434538478366494</v>
       </c>
       <c r="E95">
-        <v>-34.62755822103198</v>
+        <v>-36.26698128789584</v>
       </c>
       <c r="F95">
-        <v>-4.616345017943774</v>
+        <v>-5.318592686820892</v>
       </c>
       <c r="G95">
-        <v>-7.415609916453636</v>
+        <v>-9.230053715617387</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.973682682121912</v>
       </c>
       <c r="E96">
-        <v>-36.82046949500934</v>
+        <v>-40.56302910288551</v>
       </c>
       <c r="F96">
-        <v>-4.288947077750893</v>
+        <v>-4.8269090134899</v>
       </c>
       <c r="G96">
-        <v>-7.457084430969625</v>
+        <v>-9.060878217469552</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.504010520877258</v>
       </c>
       <c r="E97">
-        <v>-39.01259734298338</v>
+        <v>-41.6398889007245</v>
       </c>
       <c r="F97">
-        <v>-4.51726916772684</v>
+        <v>-5.067669529725708</v>
       </c>
       <c r="G97">
-        <v>-8.124407648048214</v>
+        <v>-10.04001509780102</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.015738947521739</v>
       </c>
       <c r="E98">
-        <v>-41.91782399294527</v>
+        <v>-40.99843055753799</v>
       </c>
       <c r="F98">
-        <v>-4.04758396141426</v>
+        <v>-5.22541614113897</v>
       </c>
       <c r="G98">
-        <v>-8.174178389685618</v>
+        <v>-9.16890462896151</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.477188259057516</v>
       </c>
       <c r="E99">
-        <v>-43.37672170773036</v>
+        <v>-44.58053501013739</v>
       </c>
       <c r="F99">
-        <v>-3.852872862081683</v>
+        <v>-4.635944962353253</v>
       </c>
       <c r="G99">
-        <v>-8.411845764495435</v>
+        <v>-10.35016686719318</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.888625691997921</v>
       </c>
       <c r="E100">
-        <v>-45.61309048252234</v>
+        <v>-45.79818053640084</v>
       </c>
       <c r="F100">
-        <v>-4.18588108048001</v>
+        <v>-4.59540684203575</v>
       </c>
       <c r="G100">
-        <v>-8.849744865156993</v>
+        <v>-9.414381580698468</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.215673356205828</v>
       </c>
       <c r="E101">
-        <v>-47.86298354493822</v>
+        <v>-49.15374128405551</v>
       </c>
       <c r="F101">
-        <v>-3.953950516575733</v>
+        <v>-4.677328781629601</v>
       </c>
       <c r="G101">
-        <v>-8.44439173769201</v>
+        <v>-9.60592643505516</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.495382517457861</v>
       </c>
       <c r="E102">
-        <v>-50.55215556787565</v>
+        <v>-51.46606728549664</v>
       </c>
       <c r="F102">
-        <v>-3.26543199427956</v>
+        <v>-4.105669543274832</v>
       </c>
       <c r="G102">
-        <v>-10.07529227106749</v>
+        <v>-10.30497129949105</v>
       </c>
     </row>
   </sheetData>
